--- a/www/download/IND.gdp.s.du.rpA1.xlsx
+++ b/www/download/IND.gdp.s.du.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59165.5315725644</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59712.1768454381</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59927.1255434859</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>60186.8737036746</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63786.4916364185</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66019.3489021835</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>64227.2033567898</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66251.7718684733</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72794.5942995134</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81190.5474589971</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89485.0915740802</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96647.6327664843</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112293.515770211</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134313.361650512</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131809.702931509</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26990.2222794165</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27101.7476872561</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27068.0156995343</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26911.1999785372</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27869.314499099</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28554.9608925648</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27793.0303121543</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28100.9290657467</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30363.2057373023</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33548.1240847017</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>35367.7660388559</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37004.7958621559</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42079.4290465798</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47570.411229718</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41418.7935566556</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20588.880299449</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20480.7782342563</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20434.4436884262</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20460.7134964219</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21513.4579318794</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22436.95030981</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21935.1137031236</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21995.8636485049</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23534.3870050507</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25936.230249278</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27509.3788114431</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29130.3135951071</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33326.9342494599</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37112.608504695</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33884.4984422669</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31499.8435640037</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32179.5881025717</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30973.0136799257</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29497.9394345666</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29024.5510206307</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28447.1546011474</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26674.3352102396</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>27242.0219112121</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29431.9482909534</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33308.1590027158</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36383.3576292261</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39333.0038238373</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45490.0468156036</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49645.3569709867</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45118.3906074577</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>671104.469807069</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>657805.223140609</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.661</t>
+          <t>661363.027863205</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>645781.052317799</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>699688.184250667</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>718875.101425677</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.693</t>
+          <t>692703.234896303</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>728959.207038027</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.794</t>
+          <t>793861.295832358</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>921709.917707918</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>1002083.73652181</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.049</t>
+          <t>1048720.048862</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1204786.45490188</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1369790.45817434</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.257</t>
+          <t>1257096.9139568</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85991.8394175951</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87683.113232846</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88569.9726983315</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88482.4550457263</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93442.6969921314</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97075.4062968528</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93333.9862135167</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95911.7133523789</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>104178.52775468</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117884.56226843</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>126832.747520883</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134285.916136</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>154162.049690722</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171134.424247872</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>155741.298775237</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.219</t>
+          <t>7218947.53862714</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.293</t>
+          <t>7293127.80189334</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7.274</t>
+          <t>7274388.44732156</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7.21</t>
+          <t>7210466.75049545</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.569</t>
+          <t>7569450.97100664</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7.811</t>
+          <t>7810999.29757633</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7.752</t>
+          <t>7752126.47918897</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.111</t>
+          <t>8111129.94110144</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>8.893</t>
+          <t>8892761.19874367</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9.932</t>
+          <t>9931797.32341018</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10.672</t>
+          <t>10672046.6070444</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>11.524</t>
+          <t>11524115.9615191</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>13.311</t>
+          <t>13310597.5714875</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>15.159</t>
+          <t>15158505.5274568</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14.176</t>
+          <t>14175999.5991129</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2050.73579177682</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2037.95435221457</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2011.63119782229</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1997.88010942183</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2085.05567739152</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2133.08305329444</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2089.19295049134</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2134.86406597799</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2379.3335253364</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2666.02914706164</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2869.9534597188</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3043.2632102534</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3503.33378847409</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3812.95027931042</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3600.6718350696</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49840.6230018088</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50861.1869230441</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50234.3949026717</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49025.0414242477</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49121.1104656804</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>49359.3503901714</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46174.6168339357</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46415.0943074551</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48924.1185858926</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54115.9754344342</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58586.1809515833</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62174.3768801042</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71445.8583976317</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>80806.2354809686</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71053.5536049603</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>237771.928261658</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>231843.392889937</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>226996.612756765</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226149.804277099</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>233297.26304191</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>236463.939562586</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226270.737982962</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>226396.522252217</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>239430.97098501</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264606.331465461</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279497.733207768</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>292502.961927542</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>334925.547744856</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>370200.777456715</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>333835.765950201</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17375.4431399692</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17365.4087484693</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17570.856630663</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17856.6416474719</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18712.6556279102</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19279.9266553541</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18825.7834885892</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19089.3820613919</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20154.1170860413</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21892.3274487169</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23522.7263456136</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25145.8767312381</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>28614.0804864288</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31837.1725545177</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29225.8353927982</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93863.2158703977</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95152.6888758539</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>97963.6017333144</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101469.176960096</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>110402.980461756</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>118049.345374691</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117907.049088027</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123124.679007142</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134846.819161024</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151019.786082631</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165304.75747573</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177433.294043833</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>202780.844888353</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215149.409856175</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>178967.469384399</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6088.2050384156</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5906.57330507622</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5771.1377338861</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5547.85682425672</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5378.11180566705</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5307.97593514348</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5253.48205404322</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5332.97218588564</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6013.35848489094</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6829.22267364485</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7257.77671947118</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8070.09181104541</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9288.85038975032</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10079.610968663</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7792.50068420669</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17177.8669219308</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17350.3273040876</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17733.7550174455</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17803.530210708</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18928.1121222997</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19394.2854661761</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18782.4892652337</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19147.5241429258</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20366.1444272394</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22476.5363029394</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24173.9121467651</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25709.6977804153</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29528.7472154658</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33063.9908043842</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29142.6243385052</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>137083.565702227</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137828.600998512</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135493.143351973</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134238.287080237</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140672.479165304</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>141936.473681003</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138104.338883988</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137918.378317759</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>147746.784691228</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165397.172167006</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>177155.463750075</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>186006.194113141</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>215584.078725864</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>241685.344407859</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>217338.228939998</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>164414.551526378</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165504.423609825</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165646.084519381</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164716.42215963</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169427.772503359</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171249.894760968</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166111.37165095</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>168095.686426412</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>179531.647164421</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>197771.270391006</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>213345.237243793</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>223514.595878809</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252800.988818847</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>276182.223474318</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>252308.378137296</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35826.7145918331</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35637.2211573768</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33996.1489061576</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34534.2760032046</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36778.2614046945</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37207.5451397264</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35762.4141554338</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35826.6452970723</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38292.9807264599</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41591.5188137501</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44369.4879425439</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48631.3231496409</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>55145.476550363</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59209.3578152716</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56954.9702612192</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40550.6489607387</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40781.1468952603</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40582.5269074716</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41094.3338761834</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43669.5996931575</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44608.703482241</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42080.5083008105</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42991.5829479302</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>44896.810179343</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48739.3546956135</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50749.1271357127</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53282.6415212029</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59853.7751385965</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62543.2952294104</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57733.5849305045</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>676877.336184275</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>685747.455691954</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>657812.564462933</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>672998.028602778</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>761051.227051583</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>832491.430931072</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.819</t>
+          <t>819363.69211957</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>876843.330526353</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>968395.218489516</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>1075765.52224927</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.042</t>
+          <t>1041899.53093869</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.019</t>
+          <t>1019228.10497021</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>1184148.30838317</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1321434.40190386</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.253</t>
+          <t>1252769.2227402</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5.629</t>
+          <t>5628726.30349686</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5860159.37321645</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.866</t>
+          <t>5866344.7133511</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>5.866</t>
+          <t>5866279.81049492</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.021</t>
+          <t>6021382.07148273</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6.442</t>
+          <t>6441907.14942694</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6519535.56287412</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>6520246.35826461</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>7.402</t>
+          <t>7401549.87392593</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8.363</t>
+          <t>8363035.05356652</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>9.236</t>
+          <t>9235769.0262889</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>9.748</t>
+          <t>9748283.80637503</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>10.699</t>
+          <t>10698652.2373811</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>11.892</t>
+          <t>11891798.7542964</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11.117</t>
+          <t>11117149.0280853</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11536.2730715585</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12007.6208728137</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12341.6504624857</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12834.4027842475</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14003.8379184339</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14808.3861094383</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14818.5203946491</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15103.8190556788</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16424.2600038866</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18568.7997956448</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20754.1846142988</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22827.8164600936</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26216.0992845982</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>29276.9434962183</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24829.7451497366</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158799.403756749</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>159566.639578124</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158726.485813837</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>160294.254008711</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166307.385467166</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>168025.674912375</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>165073.680199156</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>168540.805434228</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>181155.300034621</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>201071.274854678</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215120.845831983</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>228740.297155399</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>262112.786461994</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>287903.778682996</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>254489.053256419</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>528024.460794574</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.531</t>
+          <t>531415.390222256</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>523364.536310498</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>497899.510612209</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>505047.300037279</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>513290.217990783</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>488766.085236805</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>485264.690078378</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>521815.568490498</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>571763.079232766</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>601626.249178163</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>634380.351770645</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>718793.663833616</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>769729.600034026</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>661673.49648695</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>222783.020992882</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>218199.748124386</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>213414.595772775</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195130.834275412</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>208689.176797465</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218888.768075045</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>209656.584013131</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>214818.996267675</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>232549.667979935</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>265752.20165282</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272918.920873113</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>285062.483815021</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>314565.535077353</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>350405.149077876</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>325879.897796837</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13577.0283848607</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13750.9389124306</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13239.2175532253</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13839.1982938439</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13570.8357174826</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14099.8957708029</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13067.6349736233</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13398.1348409252</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14759.7099548544</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16060.6298966586</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18110.9199767544</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18588.6393588744</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21674.1237648712</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23255.639390284</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19847.3891153405</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1230.52268617658</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1268.54398347745</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1294.44589226074</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1315.86241023306</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1366.29533014659</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1472.13234459197</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1480.93258900404</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1569.18816626203</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1818.62647863145</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2054.18619001685</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2252.17922432938</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2420.76150849827</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2823.34160671452</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3364.51788649985</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3157.5599922139</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7368.09127422726</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7270.99023397967</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7460.01375795394</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7245.81651180554</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7089.25719526687</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6556.74773382901</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6243.14490043846</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6237.74596007303</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6886.23532916428</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7572.76410140211</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8268.56470628372</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8981.64727721316</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10365.3405842111</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10983.7485057449</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7510.76379548708</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>336725.669148353</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>353879.249127427</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356522.127369063</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>365043.734462284</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>391393.252094533</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>408404.400409447</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>399245.14773367</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>409727.663971958</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>455397.921739653</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>523259.971477409</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>559084.339493565</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>594120.702009083</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.674</t>
+          <t>673776.909712201</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>806510.339566124</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>737355.802218836</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1023.86667401515</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1036.08751987707</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1033.53933627398</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1042.20472572688</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1100.08620941816</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1135.54459392306</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>953.269513267911</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1150.18823937682</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1146.1176072075</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1267.67562285058</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1328.89589213644</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1405.02420891268</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1586.65941476255</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1672.29159561908</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1533.25083611942</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37568.0823486282</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38260.0509546323</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38868.4730288193</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38730.3502371831</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41158.3510155651</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42966.1446412608</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42332.1874159222</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43434.2966349242</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46542.985526975</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50580.8351460347</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53830.8791213464</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56753.3758055214</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64897.4910211152</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>73447.3701683909</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68025.2870500242</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160786.304427932</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164545.632089744</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>164524.826313148</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>162603.285619485</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163134.216390762</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>163443.563485847</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138883.083725925</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135028.14876261</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>142771.65316173</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>157866.731709067</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171171.423426143</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>182732.090567965</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>211253.801848089</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>242975.331158964</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>218633.799666345</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39539.9650062743</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39992.8871689419</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39792.9019205145</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39849.6021159928</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41963.2805853681</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43913.5993561763</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42658.8281353646</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43576.3733760261</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45595.0377376722</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49760.9333119214</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52190.4144477306</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>54957.5927299972</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>61892.7836902606</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>67484.8452533021</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60795.1266076087</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109134.666176472</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112350.906654698</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105750.051223856</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101532.390822087</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129609.357891615</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>130432.118399116</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125343.627321245</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112103.165164508</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118768.986677164</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123532.439663771</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>130621.071234164</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136961.324950057</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155405.138455521</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172151.062743367</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156030.53164202</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.863</t>
+          <t>863061.636392116</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>845199.907630108</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>801672.467882586</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>756444.056864387</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.788</t>
+          <t>788253.346213063</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>810986.212728703</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>786243.33684591</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>797736.083818014</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>855117.135877134</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>939922.614900929</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>999994.963891677</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.049</t>
+          <t>1049071.66033768</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1193020.45977261</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>1316185.48788102</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.186</t>
+          <t>1185802.87702826</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20180.4789702355</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19858.0350544545</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19371.4740726224</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18592.9244180656</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18444.7596023884</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18226.8550988599</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17424.2202456773</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16931.3349679815</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17778.5468892058</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20073.0287381668</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21414.5159638287</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22133.5088730039</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25917.2798123665</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30045.7342929785</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26846.9360817312</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9124.70511543255</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8815.24766032682</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8573.17582937315</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8400.95566132948</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8714.5046694756</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8877.21990013031</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8598.76568574199</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8673.54197831043</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9199.46203639256</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10049.4533331623</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10718.2690503158</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11242.3137213853</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12962.4485787525</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15074.8797429287</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>13312.7549055857</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30529.227175921</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30610.5480694473</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>29954.6016071986</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>30186.3303280077</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32071.0874215819</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32977.3704144147</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32392.3737200484</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32797.3003477562</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34765.1163133721</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38462.3715502257</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41038.3022554327</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43003.8819885326</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50235.5864930481</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56290.9916691364</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50915.0011554671</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>249199.707289927</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>261174.382673683</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>258888.714245876</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>247507.709345169</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>255326.459927866</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>240432.110186959</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>233920.376683405</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229846.950372963</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>240871.941264369</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>270285.63630887</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>286489.87721269</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>285844.958513112</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>302541.283359909</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>341117.864669059</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>312533.656884424</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98077.866479483</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96488.0295543096</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97420.8260615106</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95265.9928311138</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98085.8702333103</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100723.261834864</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90388.5079323237</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92133.3264670608</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>99997.6986835373</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>112809.108581469</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122538.602429538</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>129465.346954009</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>149511.25189947</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>166119.999364368</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>145371.275696418</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>729021.413603972</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>743525.354275919</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>756017.608964852</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>765198.308586843</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>805606.343523567</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>841029.734395578</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>803566.732659984</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.803</t>
+          <t>802876.51499024</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>856234.712816585</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>955981.047576001</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>1.033</t>
+          <t>1033193.40901991</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>1110555.91259791</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1255070.96077175</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>1362741.57991153</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1.193</t>
+          <t>1193133.01256049</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>10.503</t>
+          <t>10502690.5392718</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10.799</t>
+          <t>10799241.7023113</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>10.908</t>
+          <t>10908166.9034149</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11.001</t>
+          <t>11001358.342753</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11.644</t>
+          <t>11643624.5267521</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>12.359</t>
+          <t>12358999.2425764</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>12.428</t>
+          <t>12428338.8114015</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>13.114</t>
+          <t>13114018.5663406</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>14.722</t>
+          <t>14722350.3872341</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>16.696</t>
+          <t>16695607.4273276</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>18.261</t>
+          <t>18261211.0876315</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>19.862</t>
+          <t>19862016.3567659</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>22.684</t>
+          <t>22684048.1491424</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>25.879</t>
+          <t>25878655.4190609</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>24.445</t>
+          <t>24445260.6923445</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>29.352</t>
+          <t>29351918.3930971</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>29.983</t>
+          <t>29982724.0757767</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29.997</t>
+          <t>29997279.8547997</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29.936</t>
+          <t>29935814.1418096</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31450241.8988348</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>33.031</t>
+          <t>33031486.5248225</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>32.884</t>
+          <t>32884450.473856</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>34.048</t>
+          <t>34048121.3030245</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>37.821</t>
+          <t>37821400.4069326</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>42.594</t>
+          <t>42593583.1755918</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>46.198</t>
+          <t>46198087.514222</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>49.524</t>
+          <t>49523529.948326</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>56.248</t>
+          <t>56247679.2244565</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>63.571</t>
+          <t>63571268.2469141</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>59.362</t>
+          <t>59361878.9419383</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gdp.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
